--- a/data/trans_dic/P57_AC_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P57_AC_R-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con apoyo confidencial bajo (Duke)</t>
+          <t>Población con apoyo confidencial bajo (Duke) (tasa de respuesta: 99,29%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>71,34; 76,74</t>
+          <t>71,35; 76,81</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>67,54; 73,76</t>
+          <t>67,27; 73,34</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>76,21; 82,05</t>
+          <t>76,02; 81,88</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>62,07; 69,86</t>
+          <t>61,96; 69,92</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>75,6; 80,28</t>
+          <t>75,51; 79,94</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>73,32; 78,11</t>
+          <t>73,34; 78,22</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>82,49; 87,13</t>
+          <t>82,39; 87,05</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>67,03; 72,69</t>
+          <t>67,04; 72,14</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>74,57; 77,92</t>
+          <t>74,59; 77,96</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>71,79; 75,48</t>
+          <t>71,79; 75,74</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>80,34; 84,14</t>
+          <t>80,55; 84,23</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>65,8; 70,29</t>
+          <t>65,93; 70,37</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>62,33; 66,88</t>
+          <t>62,03; 66,77</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>62,83; 67,29</t>
+          <t>62,76; 67,19</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>78,58; 82,24</t>
+          <t>78,53; 82,16</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>36,95; 61,4</t>
+          <t>35,52; 61,75</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>64,89; 69,55</t>
+          <t>64,89; 69,45</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>71,29; 75,69</t>
+          <t>71,1; 75,69</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>81,43; 84,81</t>
+          <t>81,41; 84,82</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>52,33; 63,29</t>
+          <t>53,56; 63,4</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>64,11; 67,46</t>
+          <t>64,21; 67,52</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>67,44; 70,53</t>
+          <t>67,21; 70,42</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>80,54; 82,92</t>
+          <t>80,5; 82,92</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>46,24; 61,29</t>
+          <t>45,97; 60,83</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>62,71; 70,71</t>
+          <t>62,52; 70,95</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>58,39; 67,95</t>
+          <t>58,34; 67,86</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>69,74; 77,37</t>
+          <t>69,79; 77,7</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>54,11; 62,65</t>
+          <t>54,25; 62,81</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>58,0; 67,05</t>
+          <t>57,54; 66,53</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>59,11; 69,05</t>
+          <t>59,16; 68,55</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>68,46; 76,31</t>
+          <t>68,45; 76,28</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>51,33; 57,82</t>
+          <t>51,36; 58,47</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>61,84; 67,88</t>
+          <t>61,69; 67,87</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>60,63; 67,6</t>
+          <t>60,38; 67,31</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>70,06; 75,71</t>
+          <t>70,09; 75,65</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>53,66; 58,91</t>
+          <t>53,69; 59,2</t>
         </is>
       </c>
     </row>
@@ -1137,52 +1137,52 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>66,31; 69,51</t>
+          <t>66,37; 69,67</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>64,55; 67,85</t>
+          <t>64,71; 67,91</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>77,41; 80,32</t>
+          <t>77,56; 80,31</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>42,74; 61,87</t>
+          <t>44,32; 61,7</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>69,09; 72,13</t>
+          <t>69,12; 72,37</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>71,47; 74,67</t>
+          <t>71,62; 74,57</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>80,59; 83,4</t>
+          <t>80,83; 83,42</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>57,08; 63,26</t>
+          <t>56,71; 63,36</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>68,26; 70,49</t>
+          <t>68,26; 70,39</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>68,69; 70,93</t>
+          <t>68,67; 70,98</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>50,79; 61,86</t>
+          <t>52,27; 61,82</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con apoyo confidencial bajo (Duke)</t>
+          <t>Población con apoyo confidencial bajo (Duke) (tasa de respuesta: 99,29%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>736039; 791738</t>
+          <t>736167; 792507</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>649594; 709356</t>
+          <t>646955; 705347</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>573420; 617362</t>
+          <t>571982; 616032</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>314193; 353662</t>
+          <t>313648; 353929</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>994244; 1055751</t>
+          <t>993030; 1051308</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>974164; 1037709</t>
+          <t>974431; 1039179</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>814127; 860013</t>
+          <t>813229; 859184</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>495335; 537173</t>
+          <t>495400; 533111</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1750075; 1828625</t>
+          <t>1750425; 1829589</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1644221; 1728739</t>
+          <t>1644301; 1734744</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1397405; 1463507</t>
+          <t>1401113; 1465147</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>819337; 875259</t>
+          <t>821031; 876245</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1055541; 1132512</t>
+          <t>1050497; 1130738</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1226874; 1314122</t>
+          <t>1225536; 1312062</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1621007; 1696395</t>
+          <t>1619949; 1694765</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>841389; 1398233</t>
+          <t>808843; 1406198</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1028904; 1102731</t>
+          <t>1028919; 1101192</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1248401; 1325393</t>
+          <t>1245026; 1325305</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1610421; 1677291</t>
+          <t>1610022; 1677588</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1050883; 1270987</t>
+          <t>1075552; 1273263</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2102038; 2211951</t>
+          <t>2105424; 2213999</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2497826; 2612534</t>
+          <t>2489227; 2608103</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3254295; 3350508</t>
+          <t>3252768; 3350336</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1981449; 2626824</t>
+          <t>1970026; 2606910</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>344120; 388052</t>
+          <t>343119; 389365</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>278752; 324413</t>
+          <t>278510; 323951</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>380089; 421648</t>
+          <t>380338; 423452</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>345056; 399519</t>
+          <t>345936; 400580</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>276310; 319443</t>
+          <t>274122; 316966</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>268658; 313829</t>
+          <t>268891; 311597</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>372787; 415530</t>
+          <t>372748; 415365</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>337137; 379805</t>
+          <t>337318; 384051</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>634024; 695848</t>
+          <t>632411; 695823</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>565020; 629966</t>
+          <t>562693; 627297</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>763274; 824867</t>
+          <t>763615; 824232</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>694609; 762658</t>
+          <t>695041; 766347</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2170969; 2275537</t>
+          <t>2172811; 2281084</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2189613; 2301491</t>
+          <t>2194927; 2303614</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2601080; 2699068</t>
+          <t>2606043; 2698657</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1462267; 2116849</t>
+          <t>1516409; 2111078</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2333250; 2435811</t>
+          <t>2334164; 2444053</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2525973; 2638798</t>
+          <t>2531121; 2635431</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2828127; 2926737</t>
+          <t>2836470; 2927444</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1943043; 2153522</t>
+          <t>1930411; 2156794</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>4539778; 4688116</t>
+          <t>4540249; 4681898</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>4757309; 4912934</t>
+          <t>4756135; 4916123</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>5464599; 5598177</t>
+          <t>5464585; 5598072</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>3466419; 4222045</t>
+          <t>3567732; 4219693</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P57_AC_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P57_AC_R-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>66,1%</t>
+          <t>66,13%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>69,72%</t>
+          <t>70,86%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>68,25%</t>
+          <t>68,9%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>71,35; 76,81</t>
+          <t>71,15; 76,64</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>67,27; 73,34</t>
+          <t>67,43; 73,34</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>76,02; 81,88</t>
+          <t>76,22; 82,07</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>61,96; 69,92</t>
+          <t>61,97; 69,92</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>75,51; 79,94</t>
+          <t>75,75; 80,15</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>73,34; 78,22</t>
+          <t>73,41; 78,29</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>82,39; 87,05</t>
+          <t>82,35; 87,03</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>67,04; 72,14</t>
+          <t>68,38; 73,57</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>74,59; 77,96</t>
+          <t>74,57; 78,0</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>71,79; 75,74</t>
+          <t>71,75; 75,53</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>80,55; 84,23</t>
+          <t>80,54; 84,1</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>65,93; 70,37</t>
+          <t>66,5; 70,9</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>54,33%</t>
+          <t>62,46%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>60,04%</t>
+          <t>64,07%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>57,0%</t>
+          <t>63,25%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>62,03; 66,77</t>
+          <t>62,2; 66,95</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>62,76; 67,19</t>
+          <t>62,55; 67,0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>78,53; 82,16</t>
+          <t>78,52; 82,08</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>35,52; 61,75</t>
+          <t>60,04; 64,88</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>64,89; 69,45</t>
+          <t>64,83; 69,43</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>71,1; 75,69</t>
+          <t>71,14; 75,55</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>81,41; 84,82</t>
+          <t>81,59; 84,8</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>53,56; 63,4</t>
+          <t>62,24; 66,0</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>64,21; 67,52</t>
+          <t>64,33; 67,61</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>67,21; 70,42</t>
+          <t>67,23; 70,5</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>80,5; 82,92</t>
+          <t>80,59; 82,91</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>45,97; 60,83</t>
+          <t>61,6; 64,69</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>58,27%</t>
+          <t>59,23%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>54,57%</t>
+          <t>55,65%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>56,39%</t>
+          <t>57,4%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>62,52; 70,95</t>
+          <t>62,89; 71,03</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>58,34; 67,86</t>
+          <t>58,91; 68,63</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>69,79; 77,7</t>
+          <t>69,8; 77,73</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>54,25; 62,81</t>
+          <t>55,17; 63,41</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>57,54; 66,53</t>
+          <t>58,03; 66,91</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>59,16; 68,55</t>
+          <t>59,49; 70,06</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>68,45; 76,28</t>
+          <t>68,82; 76,62</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>51,36; 58,47</t>
+          <t>52,22; 59,15</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>61,69; 67,87</t>
+          <t>61,99; 67,87</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>60,38; 67,31</t>
+          <t>60,38; 67,22</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>70,09; 75,65</t>
+          <t>70,47; 75,72</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>53,69; 59,2</t>
+          <t>54,85; 60,02</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>56,81%</t>
+          <t>62,41%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>61,09%</t>
+          <t>63,89%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>58,94%</t>
+          <t>63,17%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>66,37; 69,67</t>
+          <t>66,57; 69,65</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>64,71; 67,91</t>
+          <t>64,59; 68,12</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>77,56; 80,31</t>
+          <t>77,62; 80,34</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>44,32; 61,7</t>
+          <t>60,43; 64,25</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>69,12; 72,37</t>
+          <t>69,18; 72,21</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>71,62; 74,57</t>
+          <t>71,63; 74,65</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>80,83; 83,42</t>
+          <t>80,84; 83,31</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>56,71; 63,36</t>
+          <t>62,4; 65,3</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>68,26; 70,39</t>
+          <t>68,15; 70,43</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>68,67; 70,98</t>
+          <t>68,66; 70,98</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>79,55; 81,49</t>
+          <t>79,6; 81,49</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>52,27; 61,82</t>
+          <t>61,91; 64,4</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>334615</t>
+          <t>376421</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>515233</t>
+          <t>569337</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>849847</t>
+          <t>945759</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>736167; 792507</t>
+          <t>734086; 790728</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>646955; 705347</t>
+          <t>648516; 705384</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>571982; 616032</t>
+          <t>573473; 617453</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>313648; 353929</t>
+          <t>352715; 397948</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>993030; 1051308</t>
+          <t>996198; 1054052</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>974431; 1039179</t>
+          <t>975333; 1040139</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>813229; 859184</t>
+          <t>812763; 859030</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>495400; 533111</t>
+          <t>549434; 591096</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1750425; 1829589</t>
+          <t>1750064; 1830585</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1644301; 1734744</t>
+          <t>1643203; 1729902</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1401113; 1465147</t>
+          <t>1400858; 1462901</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>821031; 876245</t>
+          <t>912856; 973201</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1237277</t>
+          <t>1383791</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>1205705</t>
+          <t>1374046</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2442983</t>
+          <t>2757837</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1050497; 1130738</t>
+          <t>1053219; 1133779</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1225536; 1312062</t>
+          <t>1221529; 1308420</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1619949; 1694765</t>
+          <t>1619785; 1693188</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>808843; 1406198</t>
+          <t>1330359; 1437415</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1028919; 1101192</t>
+          <t>1027830; 1100844</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1245026; 1325305</t>
+          <t>1245641; 1322852</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1610022; 1677588</t>
+          <t>1613586; 1677039</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1075552; 1273263</t>
+          <t>1334730; 1415451</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2105424; 2213999</t>
+          <t>2109476; 2216860</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2489227; 2608103</t>
+          <t>2490244; 2611411</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3252768; 3350336</t>
+          <t>3256417; 3350146</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1970026; 2606910</t>
+          <t>2685689; 2820584</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>371612</t>
+          <t>415344</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>358446</t>
+          <t>406122</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>730057</t>
+          <t>821467</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>343119; 389365</t>
+          <t>345112; 389794</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>278510; 323951</t>
+          <t>281227; 327656</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>380338; 423452</t>
+          <t>380400; 423630</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>345936; 400580</t>
+          <t>386895; 444693</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>274122; 316966</t>
+          <t>276479; 318751</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>268891; 311597</t>
+          <t>270373; 318456</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>372748; 415365</t>
+          <t>374729; 417208</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>337318; 384051</t>
+          <t>381053; 431640</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>632411; 695823</t>
+          <t>635490; 695843</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>562693; 627297</t>
+          <t>562743; 626473</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>763615; 824232</t>
+          <t>767751; 825025</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>695041; 766347</t>
+          <t>784882; 858907</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1943503</t>
+          <t>2175557</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>2079384</t>
+          <t>2349505</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>4022886</t>
+          <t>4525062</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2172811; 2281084</t>
+          <t>2179290; 2280419</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2194927; 2303614</t>
+          <t>2190961; 2310541</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2606043; 2698657</t>
+          <t>2608273; 2699653</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1516409; 2111078</t>
+          <t>2106635; 2239873</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2334164; 2444053</t>
+          <t>2336294; 2438619</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2531121; 2635431</t>
+          <t>2531503; 2638353</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2836470; 2927444</t>
+          <t>2836967; 2923631</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1930411; 2156794</t>
+          <t>2294906; 2401690</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>4540249; 4681898</t>
+          <t>4532346; 4684354</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>4756135; 4916123</t>
+          <t>4755446; 4916049</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>5464585; 5598072</t>
+          <t>5467893; 5597998</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>3567732; 4219693</t>
+          <t>4435056; 4613375</t>
         </is>
       </c>
     </row>
